--- a/sheets/조재수대금교본/검수/간양록.xlsx
+++ b/sheets/조재수대금교본/검수/간양록.xlsx
@@ -2778,7 +2778,7 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
-–ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -2803,7 +2803,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -2836,11 +2836,7 @@
         </is>
       </c>
       <c r="I4" s="23"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="23"/>
       <c r="L4" s="21"/>
       <c r="M4" s="23"/>
@@ -2850,31 +2846,22 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳湳
-–ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㳞
-–
-ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="E5" s="24"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="24"/>
       <c r="H5" s="21"/>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21"/>
       <c r="M5" s="24"/>
@@ -2900,12 +2887,7 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-Z</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -2916,7 +2898,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -2931,7 +2913,7 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="I7" s="23"/>
@@ -2942,50 +2924,32 @@
     </row>
     <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
     <row r="9" ht="90.2" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -2999,25 +2963,25 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -3067,7 +3031,7 @@
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞ʒ</t>
+㳞</t>
         </is>
       </c>
       <c r="C11" s="24"/>
@@ -3081,32 +3045,28 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-㳞
-ﾉ</t>
+㳞</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-㳞
-ﾉ</t>
+㳞</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-㳞
-ﾉ</t>
+㳞</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-㳞
-ﾉ</t>
+㳞</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -3115,7 +3075,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -3128,7 +3088,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽∼</t>
+          <t xml:space="preserve">汰∼</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3140,7 +3100,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -3187,35 +3147,15 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/간양록.xlsx
+++ b/sheets/조재수대금교본/검수/간양록.xlsx
@@ -2778,7 +2778,7 @@
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -2803,7 +2803,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -2836,7 +2836,11 @@
         </is>
       </c>
       <c r="I4" s="23"/>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K4" s="23"/>
       <c r="L4" s="21"/>
       <c r="M4" s="23"/>
@@ -2846,14 +2850,15 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳湳
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㳞
-–</t>
+–
+ﾉ</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -2887,7 +2892,12 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+Z</t>
+        </is>
+      </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -2898,7 +2908,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">Z∼</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -2913,7 +2923,7 @@
       <c r="G7" s="23"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">Z∼</t>
         </is>
       </c>
       <c r="I7" s="23"/>
@@ -2949,7 +2959,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -2963,25 +2973,25 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -3031,7 +3041,7 @@
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞</t>
+㳞ʒ</t>
         </is>
       </c>
       <c r="C11" s="24"/>
@@ -3045,28 +3055,32 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-㳞</t>
+㳞
+ﾉ</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-㳞</t>
+㳞
+ﾉ</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-㳞</t>
+㳞
+ﾉ</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-㳞</t>
+㳞
+ﾉ</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -3075,7 +3089,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -3088,7 +3102,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∼</t>
+          <t xml:space="preserve">汰∽∼</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3100,7 +3114,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="K12" s="22"/>

--- a/sheets/조재수대금교본/검수/간양록.xlsx
+++ b/sheets/조재수대금교본/검수/간양록.xlsx
@@ -2730,17 +2730,17 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.63" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="11.63" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
